--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563745288</v>
+        <v>46157.93081248728</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93081248728</v>
+        <v>46157.93160574522</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93160574522</v>
+        <v>46157.93395600076</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395600076</v>
+        <v>46157.93712560082</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93712560082</v>
+        <v>46158.28212290916</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212290916</v>
+        <v>46158.29673441246</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673441246</v>
+        <v>46158.29809013524</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809013524</v>
+        <v>46158.33383093945</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383093945</v>
+        <v>46158.3685111856</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/18. ООО ТД РУСОЙЛ/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685111856</v>
+        <v>46158.37283304331</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
